--- a/artfynd/A 13109-2026 artfynd.xlsx
+++ b/artfynd/A 13109-2026 artfynd.xlsx
@@ -1815,10 +1815,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96850449</v>
+        <v>137428679</v>
       </c>
       <c r="B10" t="n">
-        <v>43428</v>
+        <v>43487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1853,11 +1853,10 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hansjön S, Upl</t>
@@ -1870,7 +1869,7 @@
         <v>6651227</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1894,12 +1893,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1908,6 +1907,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1921,20 +1921,25 @@
           <t>Viburnum opulus</t>
         </is>
       </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Viburnum opulus</t>
+          <t>Viburnum opulus # 2 m upp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1944,7 +1949,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96850449</t>
+          <t>https://artportalen.se/Sighting/137428679</t>
         </is>
       </c>
     </row>
